--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_228_R23.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_228_R23.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.2549</v>
+        <v>7.0344</v>
       </c>
       <c r="E2" t="n">
-        <v>7.0794</v>
+        <v>3.9261</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1755</v>
+        <v>3.1083</v>
       </c>
       <c r="G2" t="n">
         <v>3.5099</v>
@@ -610,13 +610,13 @@
         <v>1.6237</v>
       </c>
       <c r="S2" t="n">
-        <v>5.1213</v>
+        <v>1.9008</v>
       </c>
       <c r="T2" t="n">
-        <v>5.0563</v>
+        <v>1.903</v>
       </c>
       <c r="U2" t="n">
-        <v>0.065</v>
+        <v>-0.0022</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.53</v>
+        <v>6.8618</v>
       </c>
       <c r="E3" t="n">
-        <v>7.462</v>
+        <v>7.0962</v>
       </c>
       <c r="F3" t="n">
-        <v>0.068</v>
+        <v>-0.2344</v>
       </c>
       <c r="G3" t="n">
         <v>2.7449</v>
@@ -688,13 +688,13 @@
         <v>2.7834</v>
       </c>
       <c r="S3" t="n">
-        <v>1.017</v>
+        <v>0.3488</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6765</v>
+        <v>0.3108</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3405</v>
+        <v>0.038</v>
       </c>
       <c r="V3" t="n">
         <v>2.1444</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.6514</v>
+        <v>5.4652</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4161</v>
+        <v>5.2299</v>
       </c>
       <c r="F4" t="n">
         <v>0.2353</v>
@@ -766,10 +766,10 @@
         <v>2.0876</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0341</v>
+        <v>-0.2203</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6721</v>
+        <v>0.1417</v>
       </c>
       <c r="U4" t="n">
         <v>-0.362</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6531</v>
+        <v>4.0321</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5535</v>
+        <v>2.7645</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0996</v>
+        <v>1.2676</v>
       </c>
       <c r="G5" t="n">
         <v>2.5025</v>
@@ -844,13 +844,13 @@
         <v>2.3195</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8984</v>
+        <v>0.4806</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5149</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3835</v>
+        <v>-0.2155</v>
       </c>
       <c r="V5" t="n">
         <v>-0.1107</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. DE LARREA</t>
+          <t>D. THOMPSON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0344</v>
+        <v>1.8216</v>
       </c>
       <c r="E6" t="n">
-        <v>3.1037</v>
+        <v>-2.254</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0693</v>
+        <v>4.0755</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.371</v>
+        <v>0.4879</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2245</v>
+        <v>0.6519</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5955</v>
+        <v>-0.1641</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6082</v>
+        <v>-0.8704</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5714</v>
+        <v>-0.0805</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0368</v>
+        <v>-0.7899</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9792</v>
+        <v>1.3583</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3469</v>
+        <v>0.7324000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6323</v>
+        <v>0.6258</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.3917</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.5515</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3333</v>
+        <v>-0.058</v>
       </c>
       <c r="T6" t="n">
-        <v>1.4233</v>
+        <v>-0.2238</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0901</v>
+        <v>0.1658</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6708</v>
+        <v>1.7468</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2263</v>
+        <v>1.7728</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4445</v>
+        <v>-0.026</v>
       </c>
       <c r="G7" t="n">
         <v>0.4107</v>
@@ -1000,13 +1000,13 @@
         <v>1.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>0.492</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7468</v>
+        <v>-0.2003</v>
       </c>
       <c r="U7" t="n">
-        <v>1.2388</v>
+        <v>0.7683</v>
       </c>
       <c r="V7" t="n">
         <v>0.5361</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. THOMPSON</t>
+          <t>S. DE LARREA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.78</v>
+        <v>1.3096</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.9931</v>
+        <v>2.278</v>
       </c>
       <c r="F8" t="n">
-        <v>3.7731</v>
+        <v>-0.9685</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4879</v>
+        <v>-0.371</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6519</v>
+        <v>0.2245</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1641</v>
+        <v>-0.5955</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.8704</v>
+        <v>0.6082</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.0805</v>
+        <v>0.5714</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7899</v>
+        <v>0.0368</v>
       </c>
       <c r="M8" t="n">
-        <v>1.3583</v>
+        <v>-0.9792</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7324000000000001</v>
+        <v>-0.3469</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6258</v>
+        <v>-0.6323</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3917</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.5515</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0996</v>
+        <v>0.6084000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.963</v>
+        <v>0.5977</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1366</v>
+        <v>0.0108</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.507</v>
+        <v>-0.1225</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5418</v>
+        <v>-1.9557</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0348</v>
+        <v>1.8332</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1541</v>
+        <v>1.7008</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4214</v>
+        <v>0.8643</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7327</v>
+        <v>0.8365</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4036</v>
+        <v>1.3505</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2724</v>
+        <v>0.4572</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6758999999999999</v>
+        <v>0.8932</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7504999999999999</v>
+        <v>0.3503</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6938</v>
+        <v>0.4071</v>
       </c>
       <c r="O9" t="n">
         <v>-0.0568</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9278</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3195</v>
+        <v>-3.4793</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8971</v>
+        <v>0.0323</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5034</v>
+        <v>0.1731</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3936</v>
+        <v>-0.1408</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9117</v>
+        <v>-1.3313</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5769</v>
+        <v>-1.8956</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6652</v>
+        <v>0.5643</v>
       </c>
       <c r="G10" t="n">
-        <v>1.7008</v>
+        <v>-1.1541</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8643</v>
+        <v>-0.4214</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8365</v>
+        <v>-0.7327</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3505</v>
+        <v>-0.4036</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4572</v>
+        <v>0.2724</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8932</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3503</v>
+        <v>-0.7504999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4071</v>
+        <v>-0.6938</v>
       </c>
       <c r="O10" t="n">
         <v>-0.0568</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.8556</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.4793</v>
+        <v>-2.3195</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7569</v>
+        <v>0.0727</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4481</v>
+        <v>0.1496</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3088</v>
+        <v>-0.0769</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8201</v>
+        <v>-1.7935</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9087</v>
+        <v>-2.319</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0886</v>
+        <v>0.5255</v>
       </c>
       <c r="G11" t="n">
         <v>-2.3054</v>
@@ -1312,13 +1312,13 @@
         <v>2.3195</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.5327</v>
+        <v>-0.5061</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8804</v>
+        <v>-0.2906</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6524</v>
+        <v>-0.2155</v>
       </c>
       <c r="V11" t="n">
         <v>-0.1418</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.6853</v>
+        <v>-3.6073</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.8208</v>
+        <v>-4.8771</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1354</v>
+        <v>1.2698</v>
       </c>
       <c r="G12" t="n">
         <v>-3.0636</v>
@@ -1390,13 +1390,13 @@
         <v>1.6237</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5316</v>
+        <v>0.5465</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5816</v>
+        <v>0.362</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0501</v>
+        <v>0.1845</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3943</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.4811</v>
+        <v>-5.1273</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.7214</v>
+        <v>-4.3675</v>
       </c>
       <c r="F13" t="n">
         <v>-0.7598</v>
@@ -1468,10 +1468,10 @@
         <v>2.3195</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4718</v>
+        <v>0.8257</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0193</v>
+        <v>0.3345</v>
       </c>
       <c r="U13" t="n">
         <v>0.4911</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>15.1694</v>
+        <v>16.2896</v>
       </c>
       <c r="E14" t="n">
-        <v>4.278299999999999</v>
+        <v>5.398600000000004</v>
       </c>
       <c r="F14" t="n">
-        <v>10.8909</v>
+        <v>10.8908</v>
       </c>
       <c r="G14" t="n">
         <v>7.9194</v>
@@ -1516,13 +1516,13 @@
         <v>8.186899999999998</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2676999999999998</v>
+        <v>-0.2677000000000007</v>
       </c>
       <c r="J14" t="n">
         <v>11.7788</v>
       </c>
       <c r="K14" t="n">
-        <v>9.889600000000002</v>
+        <v>9.8896</v>
       </c>
       <c r="L14" t="n">
         <v>1.889200000000001</v>
@@ -1537,7 +1537,7 @@
         <v>-2.1569</v>
       </c>
       <c r="P14" t="n">
-        <v>4.6392</v>
+        <v>4.639200000000001</v>
       </c>
       <c r="Q14" t="n">
         <v>-17.3966</v>
@@ -1546,19 +1546,19 @@
         <v>22.0355</v>
       </c>
       <c r="S14" t="n">
-        <v>3.479199999999999</v>
+        <v>4.5994</v>
       </c>
       <c r="T14" t="n">
-        <v>2.8333</v>
+        <v>3.9538</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6456999999999999</v>
+        <v>0.6455999999999998</v>
       </c>
       <c r="V14" t="n">
         <v>-0.8682999999999996</v>
       </c>
       <c r="W14" t="n">
-        <v>7.062500000000002</v>
+        <v>7.0625</v>
       </c>
       <c r="X14" t="n">
         <v>-7.9308</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.007</v>
+        <v>5.2309</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6003</v>
+        <v>3.308</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4068</v>
+        <v>1.9229</v>
       </c>
       <c r="G15" t="n">
         <v>3.6355</v>
@@ -1624,13 +1624,13 @@
         <v>2.7834</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.4145</v>
+        <v>-0.1907</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1949</v>
+        <v>-0.4872</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2196</v>
+        <v>0.2965</v>
       </c>
       <c r="V15" t="n">
         <v>0.3943</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. DOKOSSI</t>
+          <t>J. MORGAN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.0692</v>
+        <v>2.7392</v>
       </c>
       <c r="E16" t="n">
-        <v>1.657</v>
+        <v>2.0446</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4122</v>
+        <v>0.6946</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0392</v>
+        <v>1.1878</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.6338</v>
+        <v>-1.2413</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6731</v>
+        <v>2.4291</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9366</v>
+        <v>1.2449</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5749</v>
+        <v>-0.7156</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3618</v>
+        <v>1.9606</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8974</v>
+        <v>-0.0572</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2087</v>
+        <v>-0.5256999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3113</v>
+        <v>0.4685</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.5515</v>
+        <v>-0.232</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0876</v>
+        <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>1.5635</v>
+        <v>0.4639</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0578</v>
+        <v>0.4955</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5056</v>
+        <v>-0.0316</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9304</v>
+        <v>-0.5361</v>
       </c>
       <c r="W16" t="n">
-        <v>1.214</v>
+        <v>0.5361</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2836</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. MORGAN</t>
+          <t>A. DOKOSSI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.2903</v>
+        <v>2.2163</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0446</v>
+        <v>0.9493</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2456</v>
+        <v>1.267</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1878</v>
+        <v>1.0392</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.2413</v>
+        <v>-0.6338</v>
       </c>
       <c r="I17" t="n">
-        <v>2.4291</v>
+        <v>1.6731</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2449</v>
+        <v>1.9366</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.7156</v>
+        <v>0.5749</v>
       </c>
       <c r="L17" t="n">
-        <v>1.9606</v>
+        <v>1.3618</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0572</v>
+        <v>-0.8974</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5256999999999999</v>
+        <v>-1.2087</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4685</v>
+        <v>0.3113</v>
       </c>
       <c r="P17" t="n">
-        <v>1.6237</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.232</v>
+        <v>-2.5515</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8556</v>
+        <v>2.0876</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0149</v>
+        <v>0.7106</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4955</v>
+        <v>0.3501</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4806</v>
+        <v>0.3605</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.5361</v>
+        <v>0.9304</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5361</v>
+        <v>1.214</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0722</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. CAVALIERE</t>
+          <t>Y. OUATTARA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4032</v>
+        <v>1.2604</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3784</v>
+        <v>0.9948</v>
       </c>
       <c r="F18" t="n">
-        <v>2.7816</v>
+        <v>0.2656</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.8777</v>
+        <v>-0.4497</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2365</v>
+        <v>0.1693</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.1142</v>
+        <v>-0.619</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.8205</v>
+        <v>0.6261</v>
       </c>
       <c r="K18" t="n">
-        <v>0.605</v>
+        <v>0.8739</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.4255</v>
+        <v>-0.2477</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0572</v>
+        <v>-1.0759</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3684</v>
+        <v>-0.7045</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3113</v>
+        <v>-0.3713</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0876</v>
+        <v>1.3917</v>
       </c>
       <c r="S18" t="n">
-        <v>1.4743</v>
+        <v>-0.7538</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8338</v>
+        <v>-0.7035</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6405</v>
+        <v>-0.0503</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1107</v>
+        <v>1.0722</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X18" t="n">
-        <v>0.1107</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Y. OUATTARA</t>
+          <t>L. CAVALIERE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8399</v>
+        <v>0.7919</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8769</v>
+        <v>-1.9682</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0369</v>
+        <v>2.7601</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4497</v>
+        <v>-0.8777</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1693</v>
+        <v>0.2365</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.619</v>
+        <v>-1.1142</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6261</v>
+        <v>-0.8205</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8739</v>
+        <v>0.605</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.2477</v>
+        <v>-1.4255</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0759</v>
+        <v>-0.0572</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7045</v>
+        <v>-0.3684</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3713</v>
+        <v>0.3113</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3917</v>
+        <v>2.0876</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1742</v>
+        <v>0.863</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8215</v>
+        <v>0.244</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3528</v>
+        <v>0.619</v>
       </c>
       <c r="V19" t="n">
-        <v>1.0722</v>
+        <v>0.1107</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.1107</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0374</v>
+        <v>-1.2555</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0496</v>
+        <v>-1.9316</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0122</v>
+        <v>0.6762</v>
       </c>
       <c r="G20" t="n">
         <v>1.2053</v>
@@ -2014,13 +2014,13 @@
         <v>0.4639</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2908</v>
+        <v>0.0727</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4481</v>
+        <v>-0.3301</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7389</v>
+        <v>0.4028</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6778999999999999</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7023</v>
+        <v>-1.9668</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8202</v>
+        <v>0.2305</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.5225</v>
+        <v>-2.1972</v>
       </c>
       <c r="G21" t="n">
         <v>-0.315</v>
@@ -2092,13 +2092,13 @@
         <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2456</v>
+        <v>-0.51</v>
       </c>
       <c r="T21" t="n">
-        <v>0.8338</v>
+        <v>0.244</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.0794</v>
+        <v>-0.7541</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6778999999999999</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5109</v>
+        <v>-2.9326</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.3515</v>
+        <v>-0.9413</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.1593</v>
+        <v>-1.9913</v>
       </c>
       <c r="G22" t="n">
         <v>-0.9483</v>
@@ -2170,13 +2170,13 @@
         <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1709</v>
+        <v>-0.5926</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5351</v>
+        <v>-0.0547</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7059</v>
+        <v>-0.5379</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4684</v>
+        <v>-2.9965</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4959</v>
+        <v>-0.0241</v>
       </c>
       <c r="F23" t="n">
         <v>-2.9725</v>
@@ -2248,10 +2248,10 @@
         <v>0.4639</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3328</v>
+        <v>-0.861</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4402</v>
+        <v>0.0316</v>
       </c>
       <c r="U23" t="n">
         <v>-0.8927</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>N. HIFI</t>
+          <t>S. HERRERA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.066</v>
+        <v>-3.5811</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.6884</v>
+        <v>-4.8161</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.3776</v>
+        <v>1.235</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.2747</v>
+        <v>-2.4989</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.0625</v>
+        <v>-1.6589</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.2122</v>
+        <v>-0.84</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.8619</v>
+        <v>-2.0841</v>
       </c>
       <c r="K24" t="n">
-        <v>1.0321</v>
+        <v>-0.6183</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.894</v>
+        <v>-1.4658</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.4127</v>
+        <v>-0.4148</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.0945</v>
+        <v>-1.0406</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.3182</v>
+        <v>0.6258</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.3917</v>
+        <v>-2.5515</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6959</v>
+        <v>2.7834</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1677</v>
+        <v>-0.1002</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.507</v>
+        <v>-0.1806</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6607</v>
+        <v>0.0804</v>
       </c>
       <c r="V24" t="n">
-        <v>1.0722</v>
+        <v>-1.214</v>
       </c>
       <c r="W24" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S. HERRERA</t>
+          <t>N. HIFI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.805</v>
+        <v>-3.5942</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.5238</v>
+        <v>-1.2166</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7188</v>
+        <v>-2.3776</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.4989</v>
+        <v>-3.2747</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.6589</v>
+        <v>-0.0625</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.84</v>
+        <v>-3.2122</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.0841</v>
+        <v>-0.8619</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.6183</v>
+        <v>1.0321</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.4658</v>
+        <v>-1.894</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.4148</v>
+        <v>-2.4127</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.0406</v>
+        <v>-1.0945</v>
       </c>
       <c r="O25" t="n">
-        <v>0.6258</v>
+        <v>-1.3182</v>
       </c>
       <c r="P25" t="n">
-        <v>0.232</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.5515</v>
+        <v>-1.3917</v>
       </c>
       <c r="R25" t="n">
-        <v>2.7834</v>
+        <v>0.6959</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.3241</v>
+        <v>-0.6959</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8883</v>
+        <v>-0.0351</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4358</v>
+        <v>-0.6607</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.214</v>
+        <v>1.0722</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-9.189</v>
+        <v>-9.508599999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.4022</v>
+        <v>-7.5202</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.7868</v>
+        <v>-1.9884</v>
       </c>
       <c r="G26" t="n">
         <v>-3.9487</v>
@@ -2482,13 +2482,13 @@
         <v>0.6959</v>
       </c>
       <c r="S26" t="n">
-        <v>0.007</v>
+        <v>-0.3126</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1019</v>
+        <v>-0.2199</v>
       </c>
       <c r="U26" t="n">
-        <v>0.109</v>
+        <v>-0.0927</v>
       </c>
       <c r="V26" t="n">
         <v>-1.0722</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-15.1694</v>
+        <v>-13.5966</v>
       </c>
       <c r="E27" t="n">
-        <v>-10.8908</v>
+        <v>-10.8909</v>
       </c>
       <c r="F27" t="n">
-        <v>-4.278400000000001</v>
+        <v>-2.7056</v>
       </c>
       <c r="G27" t="n">
         <v>-7.9194</v>
@@ -2530,7 +2530,7 @@
         <v>-8.1867</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2675999999999995</v>
+        <v>0.2676000000000005</v>
       </c>
       <c r="J27" t="n">
         <v>3.8593</v>
@@ -2560,13 +2560,13 @@
         <v>17.3965</v>
       </c>
       <c r="S27" t="n">
-        <v>-3.4793</v>
+        <v>-1.9066</v>
       </c>
       <c r="T27" t="n">
         <v>-0.6459</v>
       </c>
       <c r="U27" t="n">
-        <v>-2.8335</v>
+        <v>-1.2608</v>
       </c>
       <c r="V27" t="n">
         <v>0.8682000000000003</v>
